--- a/informed_consent_forms/010_dance_studio_covid_19_release_form--informed_consent_forms.xlsx
+++ b/informed_consent_forms/010_dance_studio_covid_19_release_form--informed_consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1351,7 +1351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>runny_nose</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sore Throat</t>
+          <t>Runny Nose</t>
         </is>
       </c>
     </row>
@@ -1962,12 +1962,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>runny_nose</t>
+          <t>sore_or_swollen_eyes</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Runny Nose</t>
+          <t>Sore or swollen eyes</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>sore_or_swollen_eyes</t>
+          <t>sore_throat</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sore or swollen eyes</t>
+          <t>Sore throat</t>
         </is>
       </c>
     </row>
@@ -1996,12 +1996,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>nose_or_facial_pressure</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sore throat</t>
+          <t>Nose or facial pressure</t>
         </is>
       </c>
     </row>
@@ -2013,29 +2013,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nose_or_facial_pressure</t>
+          <t>other_(please_describe)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nose or facial pressure</t>
+          <t>Other (Please describe)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>student_consent_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>other_(please_describe)</t>
+          <t>i_understand_and_agree_to_the_terms</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Other (Please describe)</t>
+          <t>I understand and agree to the terms</t>
         </is>
       </c>
     </row>
@@ -2047,29 +2047,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>i_understand_and_agree_to_the_terms</t>
+          <t>i_do_not_understand_or_do_not_agree</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>I understand and agree to the terms</t>
+          <t>I do not understand or do not agree</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>student_consent_choices</t>
+          <t>adult_consent_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>i_do_not_understand_or_do_not_agree</t>
+          <t>i_am_the_adult</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>I do not understand or do not agree</t>
+          <t>I am the adult</t>
         </is>
       </c>
     </row>
@@ -2081,29 +2081,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>i_am_the_adult</t>
+          <t>i_am_not_the_adult</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>I am the adult</t>
+          <t>I am not the adult</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>adult_consent_2_choices</t>
+          <t>guardian_consent_2_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>i_am_not_the_adult</t>
+          <t>i_am_the_guardian</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>I am not the adult</t>
+          <t>I am the guardian</t>
         </is>
       </c>
     </row>
@@ -2115,29 +2115,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>i_am_the_guardian</t>
+          <t>i_am_not_the_guardian</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>I am the guardian</t>
+          <t>I am not the guardian</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>guardian_consent_2_choices</t>
+          <t>adult_consent_3_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>i_am_not_the_guardian</t>
+          <t>i_am_the_adult</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>I am not the guardian</t>
+          <t>I am the adult</t>
         </is>
       </c>
     </row>
@@ -2149,27 +2149,10 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>i_am_the_adult</t>
+          <t>i_am_not_the_adult</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
-        <is>
-          <t>I am the adult</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>adult_consent_3_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>i_am_not_the_adult</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
         <is>
           <t>I am not the adult</t>
         </is>
